--- a/Training_Plan/RCP_Training_Plan_19-30_Oct_2026.xlsx
+++ b/Training_Plan/RCP_Training_Plan_19-30_Oct_2026.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Thines, Areez, Farizal and Darwin</t>
+          <t>Thines, Areez, Farizal, Darwin and Gun Ho</t>
         </is>
       </c>
       <c r="C7" s="17" t="n"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>All four attend common modules.</t>
+          <t>All five attend common modules.</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
     <row r="3" ht="27" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Trainer: Park Jae Min | All sessions: Thines, Areez, Farizal, Darwin | Proposed times: MYT</t>
+          <t>Trainer: Park Jae Min | All sessions: Thines, Areez, Farizal, Darwin, Gun Ho | Proposed times: MYT</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Four individual practical slots (45 min each) in the morning; afternoon: targeted retest, handover of setup guide, map change checklist and fault guide</t>
+          <t>Five individual practical slots (45 min each) in the morning; afternoon: targeted retest, handover of setup guide, map change checklist and fault guide</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -1487,14 +1487,14 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>Practice rotation: Thines + Areez / Farizal + Darwin. Rotate operator and reviewer. All final tests are individual.</t>
+          <t>Practice rotation: Thines + Areez / Farizal + Darwin / Gun Ho rotating. Rotate operator and reviewer. All final tests are individual.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Final day proposal: four 45-minute individual practical slots in the morning; afternoon for feedback, targeted retests and handover.</t>
+          <t>Final day proposal: five 45-minute individual practical slots in the morning; afternoon for feedback, targeted retests and handover.</t>
         </is>
       </c>
     </row>
@@ -1760,17 +1760,36 @@
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="11" t="n"/>
     </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="17" t="n"/>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="17" t="n"/>
-      <c r="J10" s="17" t="n"/>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Gun Ho</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H10" s="13">
+        <f>IF(OR(B10="",C10="Pending",D10="",E10="",F10="Pending",G10="Pending"),"Pending",IF(AND(B10&gt;=10,C10="Pass",D10&gt;=70,E10&gt;=80,F10="Pass",G10="Approved"),"Pass","Follow-up required"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="11" t="n"/>
     </row>
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="17" t="n"/>
@@ -2109,18 +2128,21 @@
   <conditionalFormatting sqref="H6:H9">
     <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="Follow-up"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="Follow-up"/>
+  </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="C6:C9 F6:F9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C6:C10 F6:F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Pending,Pass,Needs practice"</formula1>
     </dataValidation>
-    <dataValidation sqref="G6:G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G6:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Pending,Approved,Not approved"</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole">
+    <dataValidation sqref="D6:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="B6:B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole">
+    <dataValidation sqref="B6:B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>

--- a/Training_Plan/RCP_Training_Plan_19-30_Oct_2026.xlsx
+++ b/Training_Plan/RCP_Training_Plan_19-30_Oct_2026.xlsx
@@ -1931,7 +1931,7 @@
       <c r="E16" s="17" t="n"/>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Park Jae Min approves after reviewing tests, evidence and catch-up work.</t>
+          <t>Trainer sign-off after reviewing tests, evidence and catch-up work.</t>
         </is>
       </c>
     </row>
